--- a/data/outputs/result.xlsx
+++ b/data/outputs/result.xlsx
@@ -461,27 +461,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2000</v>
+        <v>25</v>
       </c>
       <c r="B2" t="n">
-        <v>6.5</v>
+        <v>6.17</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2</v>
+        <v>13</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>암반</t>
+          <t>연약지반</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>수중</t>
+          <t>도심지</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>매우높음</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>고지압</t>
+          <t>지하수제어</t>
         </is>
       </c>
     </row>
@@ -539,11 +539,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>침매식</t>
+          <t>EPB TBM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5575</v>
+        <v>0.823</v>
       </c>
       <c r="C2" t="n">
         <v>95</v>
@@ -558,18 +558,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Slurry TBM</t>
+          <t>NATM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1401</v>
+        <v>0.0668</v>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>가능</t>
+          <t>추천하지 않음</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -577,18 +577,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EPB TBM</t>
+          <t>Slurry TBM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1506</v>
+        <v>0.0499</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>가능</t>
+          <t>추천하지 않음</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -596,14 +596,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NATM</t>
+          <t>개착식</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2763</v>
+        <v>0.0223</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -615,21 +615,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>개착식</t>
+          <t>침매식</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1437</v>
+        <v>0.0303</v>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>추천하지 않음</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>적용 곤란</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>수중 조건이 아니므로 침매식 적용 곤란</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/outputs/result.xlsx
+++ b/data/outputs/result.xlsx
@@ -461,22 +461,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>6.17</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>연약지반</t>
+          <t>혼합지반</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>도심지</t>
+          <t>도시복합</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>지하수제어</t>
+          <t>수밀성확보</t>
         </is>
       </c>
     </row>
@@ -539,11 +539,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EPB TBM</t>
+          <t>개착식</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.823</v>
+        <v>0.7111</v>
       </c>
       <c r="C2" t="n">
         <v>95</v>
@@ -558,18 +558,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NATM</t>
+          <t>EPB TBM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0668</v>
+        <v>0.4184</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>추천하지 않음</t>
+          <t>적합</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -577,14 +577,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Slurry TBM</t>
+          <t>NATM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0499</v>
+        <v>0.0595</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -596,14 +596,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>개착식</t>
+          <t>Slurry TBM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0223</v>
+        <v>0.0531</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0303</v>
+        <v>0.0305</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/data/outputs/result.xlsx
+++ b/data/outputs/result.xlsx
@@ -461,13 +461,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>7.76</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -476,22 +476,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>도시복합</t>
+          <t>하천 하부</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>매우높음</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>침하·변형관리</t>
+          <t>수압·수밀관리</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>수밀성확보</t>
+          <t>내구성·안정성</t>
         </is>
       </c>
     </row>
@@ -539,11 +539,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>개착식</t>
+          <t>Slurry TBM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7111</v>
+        <v>0.8155</v>
       </c>
       <c r="C2" t="n">
         <v>95</v>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4184</v>
+        <v>0.463</v>
       </c>
       <c r="C3" t="n">
         <v>85</v>
@@ -581,14 +581,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0595</v>
+        <v>0.089</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>추천하지 않음</t>
+          <t>가능</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -596,14 +596,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Slurry TBM</t>
+          <t>개착식</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0531</v>
+        <v>0.0213</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0305</v>
+        <v>0.0345</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/data/outputs/result.xlsx
+++ b/data/outputs/result.xlsx
@@ -461,13 +461,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>7.76</v>
+        <v>7.9</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -476,12 +476,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>하천 하부</t>
+          <t>도심지</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>매우높음</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>내구성·안정성</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -539,14 +539,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Slurry TBM</t>
+          <t>EPB TBM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8155</v>
+        <v>0.5955</v>
       </c>
       <c r="C2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -558,11 +558,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EPB TBM</t>
+          <t>Slurry TBM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.463</v>
+        <v>0.2346</v>
       </c>
       <c r="C3" t="n">
         <v>85</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.089</v>
+        <v>0.0803</v>
       </c>
       <c r="C4" t="n">
         <v>70</v>
@@ -600,14 +600,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0213</v>
+        <v>0.1665</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>추천하지 않음</t>
+          <t>가능</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0345</v>
+        <v>0.0271</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/data/outputs/result.xlsx
+++ b/data/outputs/result.xlsx
@@ -461,17 +461,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B2" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>혼합지반</t>
+          <t>암반</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>수압·수밀관리</t>
+          <t>지하수위제어</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,14 +539,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EPB TBM</t>
+          <t>NATM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5955</v>
+        <v>0.5027</v>
       </c>
       <c r="C2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -558,18 +558,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Slurry TBM</t>
+          <t>EPB TBM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2346</v>
+        <v>0.1514</v>
       </c>
       <c r="C3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>적합</t>
+          <t>가능</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -577,18 +577,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NATM</t>
+          <t>개착식</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0803</v>
+        <v>0.0221</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>가능</t>
+          <t>추천하지 않음</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -596,18 +596,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>개착식</t>
+          <t>Slurry TBM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1665</v>
+        <v>0.022</v>
       </c>
       <c r="C5" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>가능</t>
+          <t>추천하지 않음</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0271</v>
+        <v>0.0163</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
